--- a/data/seed/portfolio/L-2025-3165/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3165/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,75 +542,75 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>14365000</v>
+        <v>1721000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4856 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>73965000</v>
+        <v>61321000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>4087000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>20725000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №299/26, QQS bilan</t>
+          <t>Оплата за товар по с/ф №6114 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>69878000</v>
+        <v>82046000</v>
       </c>
     </row>
     <row r="10">
@@ -622,35 +622,35 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>21248000</v>
+        <v>7527000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2716 02.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2215 за поставленный товар</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>91126000</v>
+        <v>89573000</v>
       </c>
     </row>
     <row r="11">
@@ -662,35 +662,35 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>20265000</v>
+        <v>6019000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4737 02.07.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №4737 от 02.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>111391000</v>
+        <v>95592000</v>
       </c>
     </row>
     <row r="12">
@@ -702,75 +702,75 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>5112000</v>
+        <v>2793000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2215</t>
+          <t>Предоплата за товар по договору №139/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>116503000</v>
+        <v>98385000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n">
-        <v>12128000</v>
-      </c>
+      <c r="C13" s="2" t="n">
+        <v>2295000</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №18/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №102/26, QQS bilan</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>128631000</v>
+        <v>96090000</v>
       </c>
     </row>
     <row r="14">
@@ -780,23 +780,23 @@
       <c r="B14" t="n">
         <v>106</v>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>5145000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>5313000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -806,51 +806,51 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1637 03.07.2026, QQS bilan</t>
+          <t>Оплата за сырье по дог. №191/26 от 03.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>133776000</v>
+        <v>90777000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>3150000</v>
+        <v>4646000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Shartnoma №24/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №3768 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>136926000</v>
+        <v>95423000</v>
       </c>
     </row>
     <row r="16">
@@ -862,35 +862,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>1786000</v>
+        <v>4367000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4911 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №8457 за поставленный товар</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>138712000</v>
+        <v>99790000</v>
       </c>
     </row>
     <row r="17">
@@ -900,37 +900,37 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>6620000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>3513000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6121</t>
+          <t>Tovar uchun to'lov, h/f №2415 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>132092000</v>
+        <v>103303000</v>
       </c>
     </row>
     <row r="18">
@@ -941,36 +941,36 @@
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13260000</v>
+        <v>6066000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №188/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №37/26</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>118832000</v>
+        <v>97237000</v>
       </c>
     </row>
     <row r="19">
@@ -1001,51 +1001,51 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ish haqi, reestr №5324</t>
+          <t>ЗАРАБОТНАЯ ПЛТА ЗА ИЮНЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>96027000</v>
+        <v>74432000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1861000</v>
+        <v>41998000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qurilish Materiallari MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>336590941</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000836537074001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>Оплата за транспортные услуги по договору №269/26</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>94166000</v>
+        <v>32434000</v>
       </c>
     </row>
     <row r="21">
@@ -1055,103 +1055,103 @@
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>31071000</v>
-      </c>
-      <c r="D21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n">
+        <v>7615000</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №264/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6976</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>63095000</v>
+        <v>40049000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>17986000</v>
+        <v>1889000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №191/26, QQS 12%</t>
+          <t>Оплата по с/ф №3708 за поставленный товар</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>81081000</v>
+        <v>41938000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46211</v>
+        <v>46210</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>5923000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>4471000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1161,11 +1161,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2221 08.07.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №198/26</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>87004000</v>
+        <v>37467000</v>
       </c>
     </row>
     <row r="24">
@@ -1175,37 +1175,37 @@
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n">
-        <v>4888000</v>
-      </c>
+      <c r="C24" s="2" t="n">
+        <v>1861000</v>
+      </c>
+      <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Qarshi Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>249486951</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000058934745001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №240/26 от 08.07.2026</t>
+          <t>Аренда помещения за июль, дог. №18/25</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>91892000</v>
+        <v>35606000</v>
       </c>
     </row>
     <row r="25">
@@ -1215,23 +1215,23 @@
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>4678000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>5208000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1241,11 +1241,11 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №169/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4488</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>96570000</v>
+        <v>30398000</v>
       </c>
     </row>
     <row r="26">
@@ -1255,37 +1255,37 @@
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>1778000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>5464000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>214547327</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000020060348001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №7781</t>
+          <t>Оплата за товары согласно счет-фактуре №1179</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>98348000</v>
+        <v>24934000</v>
       </c>
     </row>
     <row r="27">
@@ -1297,35 +1297,35 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>12044000</v>
+        <v>2133000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shodlik Mato MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>239401221</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000839551536001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №165/26, QQS 12%</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №97/26 ОТ 13.07.2026</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>110392000</v>
+        <v>27067000</v>
       </c>
     </row>
     <row r="28">
@@ -1335,37 +1335,37 @@
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>5413000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>1696000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №16/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №61/26</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>115805000</v>
+        <v>25371000</v>
       </c>
     </row>
     <row r="29">
@@ -1375,37 +1375,37 @@
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>2577000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>3753000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>214547327</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000020060348001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №277/26, QQS 12%</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №8222</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>118382000</v>
+        <v>21618000</v>
       </c>
     </row>
     <row r="30">
@@ -1415,23 +1415,23 @@
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>2336000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>9983000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1441,11 +1441,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Shartnoma №67/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товары согласно счет-фактуре №3767</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>120718000</v>
+        <v>11635000</v>
       </c>
     </row>
     <row r="31">
@@ -1455,37 +1455,37 @@
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>1708000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>19251000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7472</t>
+          <t>Оплата за товары согласно счет-фактуре №4428</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>122426000</v>
+        <v>-7616000</v>
       </c>
     </row>
     <row r="32">
@@ -1496,116 +1496,116 @@
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>4124000</v>
+        <v>95032000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №172/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №1864</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>118302000</v>
+        <v>-102648000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>8260000</v>
+        <v>1252000</v>
       </c>
       <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №143/26 от 13.07.2026, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3937</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>110042000</v>
+        <v>-103900000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>10170000</v>
+        <v>1752000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №56/26</t>
+          <t>Предоплата за материалы по договору №127/26</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>99872000</v>
+        <v>-105652000</v>
       </c>
     </row>
     <row r="35">
@@ -1616,76 +1616,76 @@
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>110096000</v>
+        <v>3110000</v>
       </c>
       <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №123/26</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>-10224000</v>
+        <v>-108762000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>7460000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>3110000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SHARTNOMA №108/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>-2764000</v>
+        <v>-111872000</v>
       </c>
     </row>
     <row r="37">
@@ -1695,37 +1695,37 @@
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>3110000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>23691000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>IJTIMIY SOLIQ IYUN 2026</t>
+          <t>Оплата по счет-фактуре №1987 за поставленный товар</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>-5874000</v>
+        <v>-88181000</v>
       </c>
     </row>
     <row r="38">
@@ -1736,231 +1736,231 @@
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3110000</v>
+        <v>13800000</v>
       </c>
       <c r="D38" s="2" t="n"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>201122905</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3165)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>16307000255929856417</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>НДФЛ за июнь 2026</t>
+          <t>Kredit shartnomasi L-2025-3165 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-8984000</v>
+        <v>-101981000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>4646000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3165)</t>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>16307000255929856417</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3165 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1320</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>-22784000</v>
+        <v>-97335000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="2" t="n">
-        <v>2184000</v>
+        <v>6010000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Bog'ishamol Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>254732730</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000006034804001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №264/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №4378 за оставленный товар</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>-20600000</v>
+        <v>-91325000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>9415000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>4672000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4651</t>
+          <t>Tovar uchun to'lov, h/f №4580 20.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>-30015000</v>
+        <v>-86653000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>8424000</v>
+        <v>3357000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №55/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №143/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>-21591000</v>
+        <v>-83296000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>3405000</v>
+        <v>2688000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Shodlik Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>398545825</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000338968394001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №255/26, QQS 12%</t>
+          <t>Оплата по с/ф №5029 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>-18186000</v>
+        <v>-80608000</v>
       </c>
     </row>
     <row r="44">
@@ -1970,223 +1970,223 @@
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>8178000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>1599000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6361 20.07.2026, QQS bilan</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №157/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>-10008000</v>
+        <v>-82207000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>6484000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>3074000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Shartnoma №143/26 bo'yicha oldindan to'lov</t>
+          <t>НДС за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>-3524000</v>
+        <v>-85281000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>4694000</v>
+        <v>1913000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Saodat Plastik MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>340122188</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000955153659001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Shartnoma №27/26 bo'yicha oldindan to'lov</t>
+          <t>Mahsulot uchun to'lov, shartnoma №85/26, QQS 12%</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1170000</v>
+        <v>-83368000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>4534000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>1163000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000714387762001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №297/26, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>5704000</v>
+        <v>-84531000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n">
-        <v>3865000</v>
-      </c>
+      <c r="C48" s="2" t="n">
+        <v>3898000</v>
+      </c>
+      <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Shartnoma №279/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по дог. №254/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9569000</v>
+        <v>-88429000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>3315000</v>
+        <v>14779000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Namangan Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>267043363</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000497113235001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2196,597 +2196,592 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №254/26, QQS 12%</t>
+          <t>Оплата за продукцию по дог. №45/26, НДС 12%</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>12884000</v>
+        <v>-73650000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>3080000</v>
+        <v>8999000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8306</t>
+          <t>Оплата за товар по счет-фактуре №1624 от 27.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>15964000</v>
+        <v>-64651000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
       <c r="C51" s="2" t="n"/>
       <c r="D51" s="2" t="n">
-        <v>2644000</v>
+        <v>4441000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №136/26, QQS 12%</t>
+          <t>Предоплата за товар по дог. №219/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>18608000</v>
+        <v>-60210000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>5580000</v>
+        <v>2023000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sharq Oziq-ovqat Savdo MChJ</t>
+          <t>Saodat Plastik MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>395985458</t>
+          <t>340122188</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000503389683001</t>
+          <t>20208000955153659001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7568 21.07.2026, QQS bilan</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7781 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24188000</v>
+        <v>-58187000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46224</v>
+        <v>46231</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>2832000</v>
+        <v>25993000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Shartnoma №155/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №7643 за поставленный товар</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>27020000</v>
+        <v>-32194000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46224</v>
+        <v>46232</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>3013000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>83990000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>398545825</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000338968394001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №149/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>24007000</v>
+        <v>51796000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>15341000</v>
+        <v>1769000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf MChJ</t>
+          <t>Bog'ishamol Savdo MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>214547327</t>
+          <t>254732730</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000020060348001</t>
+          <t>20208000006034804001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4300</t>
+          <t>Предоплата за товар по дог. №139/26 от 29.07.2026</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>39348000</v>
+        <v>53565000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46225</v>
+        <v>46233</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>6844000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>2117000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3417</t>
+          <t>Mahsulot uchun to'lov, shartnoma №189/26, QQS 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>32504000</v>
+        <v>55682000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46227</v>
+        <v>46233</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>1163000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>2114000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Buxoro Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>202177164</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000001242326001</t>
+          <t>20208000109466255001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Предоплата за товар по договору №11/26 от 30.07.2026</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>31341000</v>
+        <v>57796000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>2860000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>265491908</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shartnoma №219/26 bo'yicha oldindan to'lov</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>34201000</v>
+        <v>57496000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>1855000</v>
+        <v>3910000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №235/26 от 27.07.2026</t>
+          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36056000</v>
+        <v>61406000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>1550000</v>
+        <v>2713000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №3300 ОТ 28.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №2121 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>37606000</v>
+        <v>64119000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
       <c r="C61" s="2" t="n"/>
       <c r="D61" s="2" t="n">
-        <v>8683000</v>
+        <v>1562000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sharq Oziq-ovqat Savdo MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>395985458</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000503389683001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №149/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №7134 от 03.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46289000</v>
+        <v>65681000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>6853000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>2412000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №35/26, QQS 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №5910</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>53142000</v>
+        <v>63269000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>2355000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>7191000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>214547327</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000020060348001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Shartnoma №139/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №8634</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>55497000</v>
+        <v>56078000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>2407000</v>
+        <v>1819000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2796,547 +2791,552 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №185/26 от 04.08.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>57904000</v>
+        <v>57897000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>300000</v>
+        <v>5311000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bekobod Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>390941483</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000537074600001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за сырье по дог. №16/26 от 04.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>57604000</v>
+        <v>52586000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>4159000</v>
+        <v>11511000</v>
       </c>
       <c r="D66" s="2" t="n"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1213</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №256/26</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>53445000</v>
+        <v>41075000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>20706000</v>
+        <v>4983000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Saodat Plastik MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>340122188</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000955153659001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №156/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №92/26, НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>74151000</v>
+        <v>46058000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>17135000</v>
+        <v>1710000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7838</t>
+          <t>Предоплата за товар по дог. №123/26 от 06.08.2026</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>91286000</v>
+        <v>47768000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>2899000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>23194000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>265491908</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4707 04.08.2026, QQS bilan</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>94185000</v>
+        <v>24574000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n">
-        <v>23194000</v>
-      </c>
-      <c r="D70" s="2" t="n"/>
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n">
+        <v>3814000</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №7593</t>
+          <t>Предоплата за товар по договору №96/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>70991000</v>
+        <v>28388000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>8898000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>1374000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №862</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №6803 ОТ 07.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>62093000</v>
+        <v>29762000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n">
-        <v>74333000</v>
-      </c>
-      <c r="D72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n">
+        <v>83323000</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №231/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №286/26, QQS 12%</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>-12240000</v>
+        <v>113085000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>17040000</v>
+        <v>17561000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №222/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №127/26, НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>4800000</v>
+        <v>130646000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>3346000</v>
+        <v>8011000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №163/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6310 10.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>8146000</v>
+        <v>138657000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n"/>
       <c r="D75" s="2" t="n">
-        <v>2277000</v>
+        <v>7172000</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9959 06.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №260/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>10423000</v>
+        <v>145829000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n">
-        <v>3858000</v>
-      </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n">
+        <v>4544000</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TOVARLAR UCHUN TO'LOV H/F №9778</t>
+          <t>Оплата за товар по счет-фактуре №5456 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>6565000</v>
+        <v>150373000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>7529000</v>
+        <v>1422000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Buxoro Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>202177164</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000109466255001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №756</t>
+          <t>Предоплата за товар по договору №193/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>14094000</v>
+        <v>151795000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>4252000</v>
+        <v>1893000</v>
       </c>
       <c r="D78" s="2" t="n"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Qarshi Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>249486951</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000058934745001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3346,237 +3346,237 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №58/26, QQS bilan</t>
+          <t>Арендная плата за август 2026 г. по договору №18/25</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9842000</v>
+        <v>149902000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>1893000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>28487000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qurilish Materiallari MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>336590941</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000836537074001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №64/22</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6692 11.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>7949000</v>
+        <v>178389000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>3131000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>2594000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Namangan Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>267043363</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000497113235001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №268/26</t>
+          <t>Оплата за продукцию по дог. №58/26, НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4818000</v>
+        <v>180983000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n">
-        <v>3359000</v>
-      </c>
-      <c r="D81" s="2" t="n"/>
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n">
+        <v>2394000</v>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9806</t>
+          <t>ОПЛАТА ПО С/Ф №5928 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1459000</v>
+        <v>183377000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n">
-        <v>1945000</v>
-      </c>
+      <c r="C82" s="2" t="n">
+        <v>5324000</v>
+      </c>
+      <c r="D82" s="2" t="n"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>298330221</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000606055248001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №77/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по договору №74/26</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>3404000</v>
+        <v>178053000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
-      <c r="C83" s="2" t="n">
-        <v>8559000</v>
-      </c>
-      <c r="D83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n">
+        <v>2888000</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №122/26</t>
+          <t>Предоплата за товар по договору №256/26 от 14.08.2026</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>-5155000</v>
+        <v>180941000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>10283000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>1350000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Farovon Tikuv AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>377307955</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000619924335001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9027</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №200/26, НДС 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>-15438000</v>
+        <v>182291000</v>
       </c>
     </row>
     <row r="85">
@@ -3625,7 +3625,7 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>-29238000</v>
+        <v>168491000</v>
       </c>
     </row>
     <row r="86">
@@ -3637,35 +3637,35 @@
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>11290000</v>
+        <v>2020000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8315</t>
+          <t>Tovar uchun to'lov, h/f №5417 17.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>-17948000</v>
+        <v>170511000</v>
       </c>
     </row>
     <row r="87">
@@ -3675,37 +3675,37 @@
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>4402000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>3163000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №1907</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>-13546000</v>
+        <v>167348000</v>
       </c>
     </row>
     <row r="88">
@@ -3715,37 +3715,37 @@
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>2833000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>3163000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
+          <t>НДФЛ за июль 2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>-10713000</v>
+        <v>164185000</v>
       </c>
     </row>
     <row r="89">
@@ -3756,36 +3756,36 @@
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>3163000</v>
+        <v>3887000</v>
       </c>
       <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №269/26 ОТ 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>-13876000</v>
+        <v>160298000</v>
       </c>
     </row>
     <row r="90">
@@ -3796,36 +3796,36 @@
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>3163000</v>
+        <v>5054000</v>
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi uchun</t>
+          <t>Предоплата за материалы по договору №155/26</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>-17039000</v>
+        <v>155244000</v>
       </c>
     </row>
     <row r="91">
@@ -3836,892 +3836,902 @@
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>6153000</v>
+        <v>8132000</v>
       </c>
       <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №206/26, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №157/26</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>-23192000</v>
+        <v>147112000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>5532000</v>
+        <v>9507000</v>
       </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>298330221</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000606055248001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8301</t>
+          <t>Оплата за транспортные услуги по договору №70/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>-28724000</v>
+        <v>137605000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>5559000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>13419000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Bahor Non MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>226484572</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000697271704001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4648</t>
+          <t>Оплата за сырье по договору №229/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>-23165000</v>
+        <v>124186000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n"/>
       <c r="D94" s="2" t="n">
-        <v>3967000</v>
+        <v>4546000</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Shodlik Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>398545825</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000338968394001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1268 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №3267 за поставленный товар</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>-19198000</v>
+        <v>128732000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>5807000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>3562000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №258/26</t>
+          <t>Оплата по счет-фактуре №3493 за поставленный товар</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>-25005000</v>
+        <v>132294000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46255</v>
+        <v>46253</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>15855000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>10285000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Bog'ishamol Savdo MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>254732730</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000006034804001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №4/26</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8093 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-40860000</v>
+        <v>142579000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>138031000</v>
+        <v>4455000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1813</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3418 19.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>97171000</v>
+        <v>147034000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>3056000</v>
+        <v>9788000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>QQS iyul 2026 uchun</t>
+          <t>Предоплата за материалы по договору №224/26</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>94115000</v>
+        <v>137246000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46258</v>
+        <v>46253</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>15865000</v>
+        <v>11111000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4654</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №275/26</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>78250000</v>
+        <v>126135000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>7501000</v>
+        <v>14033000</v>
       </c>
       <c r="D100" s="2" t="n"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №219/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №56</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>70749000</v>
+        <v>112102000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46260</v>
+        <v>46254</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>1183000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1800000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Shodlik Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>398545825</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000001242326001</t>
+          <t>20208000338968394001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата за товар по счет-фактуре №1651 от 20.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>69566000</v>
+        <v>113902000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>3206000</v>
+        <v>15277000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактур №4484</t>
+          <t>Оплата за сырье по договору №80/26 от 20.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>66360000</v>
+        <v>98625000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46262</v>
+        <v>46254</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>13273000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>38317000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Bekobod Meva Eksport MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>390941483</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000537074600001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5850 28.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №117/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>79633000</v>
+        <v>60308000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46262</v>
+        <v>46255</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n"/>
       <c r="D104" s="2" t="n">
-        <v>2447000</v>
+        <v>9921000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №251/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №297/26 от 21.08.2026</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>82080000</v>
+        <v>70229000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>8087000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за продукцию по дог. №236/26, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>81780000</v>
+        <v>78316000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>3038000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>3355000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №132/26</t>
+          <t>Оплата за продукцию по договору №67/26, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>78742000</v>
+        <v>81671000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>3509000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>2112000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №144/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №2810 от 24.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>75233000</v>
+        <v>83783000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>4067000</v>
+        <v>1183000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000714387762001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №207/26, QQS bilan</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>71166000</v>
+        <v>82600000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>12105000</v>
+        <v>3142000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №245/26</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>59061000</v>
+        <v>79458000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n">
-        <v>2590000</v>
-      </c>
+      <c r="C110" s="2" t="n">
+        <v>4362000</v>
+      </c>
+      <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Kattaqo'rg'on Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>298330221</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000606055248001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5831</t>
+          <t>Оплата за упаковочные материалы, с/ф №8815</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>61651000</v>
+        <v>75096000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46268</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>5203000</v>
+        <v>5478000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №57/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №34/26</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>56448000</v>
+        <v>69618000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46269</v>
+        <v>46260</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>20716000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>1529000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1400</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>35732000</v>
+        <v>71147000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46272</v>
+        <v>46261</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>9626000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>6981000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4731,117 +4741,117 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7652</t>
+          <t>Tovarlar uchun to'lov h/f №5657</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>45358000</v>
+        <v>64166000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>8391000</v>
+        <v>6814000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Buxoro Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>202177164</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000109466255001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №454</t>
+          <t>Предоплата за товар по дог. №85/26 от 28.08.2026</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>53749000</v>
+        <v>70980000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46272</v>
+        <v>46262</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>4969000</v>
+        <v>4242000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Buxoro Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>202177164</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000109466255001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Shartnoma №223/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за продукцию по договору №89/26, НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>58718000</v>
+        <v>75222000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>2152000</v>
+        <v>13206000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4851,357 +4861,352 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №175/26 от 07.09.2026</t>
+          <t>Оплата по с/ф №615 за поставленный товар</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>60870000</v>
+        <v>88428000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n"/>
       <c r="D117" s="2" t="n">
-        <v>1645000</v>
+        <v>2446000</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bog'ishamol Poligraf MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>214547327</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000020060348001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фктуре №6118 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №124/26, НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>62515000</v>
+        <v>90874000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>3009000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>1827000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №292/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3214 31.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>59506000</v>
+        <v>92701000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>1690000</v>
+        <v>300000</v>
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bog'ishamol Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>336590941</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000836537074001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>57816000</v>
+        <v>92401000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46273</v>
+        <v>46265</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4949000</v>
+        <v>7671000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №132/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №229/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>52867000</v>
+        <v>84730000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>4123000</v>
+        <v>10873000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за товры согласно счет-фактуре №8855</t>
+          <t>Предоплата за материалы по договору №80/26</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>48744000</v>
+        <v>73857000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46274</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>6215000</v>
+        <v>12901000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №623</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №83/26</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>42529000</v>
+        <v>60956000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>2194000</v>
+        <v>1696000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9174</t>
+          <t>Оплата за продукцию по договору №257/26, НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>44723000</v>
+        <v>62652000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>21467000</v>
+        <v>1286000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6828</t>
+          <t>Оплата за товары согласно счет-фактуре №8523</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>23256000</v>
+        <v>61366000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>40482000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>11503000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5211,237 +5216,237 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3035 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по дог. №109/26 от 01.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>63738000</v>
+        <v>49863000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46279</v>
+        <v>46266</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n">
-        <v>8479000</v>
-      </c>
+      <c r="C126" s="2" t="n">
+        <v>139986000</v>
+      </c>
+      <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №207/26, QQS 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №30/26</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>72217000</v>
+        <v>-90123000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46279</v>
+        <v>46268</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>7962000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>1637000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Qo'qon Mato MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>276609455</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000412818223001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №141/26, QQS 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №126/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>80179000</v>
+        <v>-91760000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>4247000</v>
+        <v>32280000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6091</t>
+          <t>Оплата за товар по с/ф №1757 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>84426000</v>
+        <v>-59480000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n">
-        <v>2179000</v>
+        <v>3176000</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1250 14.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №8287 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>86605000</v>
+        <v>-56304000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>1847000</v>
+        <v>1982000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №208/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №205/26, QQS 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>88452000</v>
+        <v>-54322000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>2512000</v>
+        <v>1690000</v>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Qarshi Qurilish Materiallari XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>249486951</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000058934745001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5451,37 +5456,32 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №8061</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №18/25</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>85940000</v>
+        <v>-56012000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46279</v>
+        <v>46272</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>3464000</v>
+        <v>20716000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>241428183</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5491,392 +5491,397 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №268/26, QQS bilan</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>82476000</v>
+        <v>-76728000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>2825000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>10839000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата по с/ф №3363 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>79651000</v>
+        <v>-65889000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>2825000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>36027000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bog'ishamol Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>254732730</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000006034804001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №283/26, QQS 12%</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>76826000</v>
+        <v>-29862000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46280</v>
+        <v>46275</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>13800000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>4237000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3165)</t>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>16307000255929856417</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3165 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №982</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>63026000</v>
+        <v>-25625000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n"/>
       <c r="D136" s="2" t="n">
-        <v>13394000</v>
+        <v>2032000</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №187/26 от 16.09.2026</t>
+          <t>Оплата за товар по счет-фактуре №7269 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>76420000</v>
+        <v>-23593000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46281</v>
+        <v>46276</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>2645000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>7347000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Shodlik Mehmonxona AJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>398545825</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000338968394001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7506</t>
+          <t>Оплата за продукцию по договору №286/26, НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>73775000</v>
+        <v>-16246000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46282</v>
+        <v>46276</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>2267000</v>
+        <v>4826000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2653 17.09.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №285/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>76042000</v>
+        <v>-11420000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n">
-        <v>3439000</v>
-      </c>
-      <c r="D139" s="2" t="n"/>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>3108000</v>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Nihol Qurilish Materiallari MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>233021771</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000421094662001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3006</t>
+          <t>Оплата за продукцию по договору №186/26, НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>72603000</v>
+        <v>-8312000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46283</v>
+        <v>46279</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>6117000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>2960000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №130/26</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №113/26 ОТ 14.09.2026</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>66486000</v>
+        <v>-5352000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>9680000</v>
+        <v>2126000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Shartnoma №189/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №35/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>76166000</v>
+        <v>-3226000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n"/>
-      <c r="D142" s="2" t="n">
-        <v>8020000</v>
-      </c>
+      <c r="C142" s="2" t="n">
+        <v>861000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Shodlik Mato MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>239401221</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000839551536001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5886,117 +5891,117 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Shartnoma №50/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за упаковочные материалы, с/ф №5678</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>84186000</v>
+        <v>-4087000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46286</v>
+        <v>46279</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n"/>
-      <c r="D143" s="2" t="n">
-        <v>3615000</v>
-      </c>
+      <c r="C143" s="2" t="n">
+        <v>3587000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Bunyodkor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>304956027</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000483015776001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2916</t>
+          <t>Оплата за транспортные услуги по договору №11/26</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>87801000</v>
+        <v>-7674000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>1620000</v>
+        <v>2089000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Angren Meva Eksport MChJ</t>
+          <t>Yulduz Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>398773079</t>
+          <t>277542784</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000576199243001</t>
+          <t>20208000456435731001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7394 21.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №3/26, QQS 12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>89421000</v>
+        <v>-5585000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>7371000</v>
+        <v>2893000</v>
       </c>
       <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,37 +6011,32 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №167/26, QQS bilan</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №8726</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>82050000</v>
+        <v>-8478000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>9023000</v>
+        <v>13800000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>241428183</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3165)</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>16307000255929856417</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6046,237 +6046,237 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №294/26</t>
+          <t>Kredit shartnomasi L-2025-3165 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>73027000</v>
+        <v>-22278000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>4019000</v>
+        <v>2796000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №6857</t>
+          <t>Оплата по с/ф №3126 за поставленный товар</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>77046000</v>
+        <v>-19482000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>8155000</v>
+        <v>2825000</v>
       </c>
       <c r="D148" s="2" t="n"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9457</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>68891000</v>
+        <v>-22307000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46288</v>
+        <v>46281</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>1056000</v>
+        <v>2825000</v>
       </c>
       <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000001242326001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за сентябрь 2026 г.</t>
+          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА АВГУСТ 2026 Г.</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>67835000</v>
+        <v>-25132000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>2792000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>15791000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>НДС ЗА АВГУСТ 2026 Г.</t>
+          <t>Оплата за товар по счет-фактуре №8031 от 17.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>65043000</v>
+        <v>-9341000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
       <c r="C151" s="2" t="n"/>
       <c r="D151" s="2" t="n">
-        <v>2181000</v>
+        <v>5153000</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Sharq Oziq-ovqat Savdo MChJ</t>
+          <t>Farovon Tikuv AJ</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>395985458</t>
+          <t>377307955</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000503389683001</t>
+          <t>20208000619924335001</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №98 24.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №190/26, QQS 12%</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>67224000</v>
+        <v>-4188000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>2842000</v>
+        <v>1465000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6286,477 +6286,477 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №525</t>
+          <t>Tovarlar uchun to'lov h/f №3105</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>64382000</v>
+        <v>-5653000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46289</v>
+        <v>46282</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>5309000</v>
+        <v>2352000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Buxoro Plastik MChJ</t>
+          <t>Farg'ona Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>241428183</t>
+          <t>221946806</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000335020256001</t>
+          <t>20208000456188332001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №51/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №13/26</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>59073000</v>
+        <v>-8005000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>44245000</v>
+        <v>3432000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Bog'ishamol Savdo MChJ</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>254732730</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000006034804001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №115/26 от 25.09.2026</t>
+          <t>Оплата по счет-фактуре №3465 за поставленный товар</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>103318000</v>
+        <v>-4573000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
       <c r="C155" s="2" t="n"/>
       <c r="D155" s="2" t="n">
-        <v>5499000</v>
+        <v>2348000</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7627 от 25.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №283/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>108817000</v>
+        <v>-2225000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>18607000</v>
+        <v>11697000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4007</t>
+          <t>Оплата по счет-фактуре №1046 за поставленный товар</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>127424000</v>
+        <v>9472000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>3875000</v>
+        <v>7671000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №16/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №168/26, НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>131299000</v>
+        <v>17143000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>3741000</v>
+        <v>6123000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Buxoro Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>202177164</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000109466255001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5612 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №5677 за поставленный товар</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>135040000</v>
+        <v>23266000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>1894000</v>
+        <v>4733000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №2653 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>136934000</v>
+        <v>27999000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n">
-        <v>4709000</v>
-      </c>
-      <c r="D160" s="2" t="n"/>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n">
+        <v>4641000</v>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Nihol Meva-Sabzavot MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>292781148</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000173667918001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №191/26, QQS bilan</t>
+          <t>Оплата за продукцию по договору №126/26, НДС 12%</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>132225000</v>
+        <v>32640000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>8892000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>3411000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Omad Mehmonxona MChJ</t>
+          <t>Saodat Plastik MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>243670433</t>
+          <t>340122188</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>20208000394971132001</t>
+          <t>20208000955153659001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №207/26, QQS bilan</t>
+          <t>Shartnoma №70/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>123333000</v>
+        <v>36051000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>12488000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>2714000</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6057</t>
+          <t>Оплата по счет-фактуре №7834 за поставленный товар</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>110845000</v>
+        <v>38765000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>48261000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>1827000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Zafar Agro Servis MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>344219468</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000684561883001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №158/26</t>
+          <t>Предоплата за товар по договору №52/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>62584000</v>
+        <v>40592000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
-      <c r="C164" s="2" t="n"/>
-      <c r="D164" s="2" t="n">
-        <v>3313000</v>
-      </c>
+      <c r="C164" s="2" t="n">
+        <v>908000</v>
+      </c>
+      <c r="D164" s="2" t="n"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Shodlik Mato MChJ</t>
+          <t>Afrosiyob Poligraf AJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>239401221</t>
+          <t>278114821</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000839551536001</t>
+          <t>20208000366791853001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6766,231 +6766,711 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №96/26, QQS 12%</t>
+          <t>Оплата за транспортные услуги по дог. №264/26</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>65897000</v>
+        <v>39684000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46294</v>
+        <v>46286</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>1746000</v>
-      </c>
+      <c r="C165" s="2" t="n">
+        <v>2825000</v>
+      </c>
+      <c r="D165" s="2" t="n"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №527 29.09.2026, QQS bilan</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>67643000</v>
+        <v>36859000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46294</v>
+        <v>46287</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
-      <c r="C166" s="2" t="n">
-        <v>16121000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n">
+        <v>5828000</v>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Omad Qurilish AJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>301983302</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000146060552001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6087</t>
+          <t>Оплата по с/ф №4671 за поставленный товар</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>51522000</v>
+        <v>42687000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="n">
-        <v>6788000</v>
+        <v>4688000</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Afrosiyob Qurilish MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>265491908</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000164096331001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №58/26 от 30.09.2026</t>
+          <t>Предоплата за товар по дог. №65/26 от 22.09.2026</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>58310000</v>
+        <v>47375000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46295</v>
+        <v>46287</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>1390000</v>
+        <v>2574000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Bog'ishamol Metall MChJ</t>
+          <t>Sharq Sut MChJ</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>312775427</t>
+          <t>349190891</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000474564357001</t>
+          <t>20208000409633144001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №120/26, QQS 12%</t>
+          <t>Shartnoma №11/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>59700000</v>
+        <v>49949000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46295</v>
+        <v>46288</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n">
+        <v>1812000</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>349190891</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>20208000409633144001</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №107/26 от 23.09.2026</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>51761000</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B170" t="n">
+        <v>262</v>
+      </c>
+      <c r="C170" s="2" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>20208000714387762001</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Оплата за электроэнергию согласно счету</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>50705000</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B171" t="n">
+        <v>263</v>
+      </c>
+      <c r="C171" s="2" t="n">
+        <v>933000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Afrosiyob Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>278114821</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>20208000366791853001</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №196/26</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>49772000</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B172" t="n">
+        <v>264</v>
+      </c>
+      <c r="C172" s="2" t="n">
+        <v>1971000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Afrosiyob Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>278114821</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>20208000366791853001</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №284/26</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>47801000</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B173" t="n">
+        <v>265</v>
+      </c>
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n">
+        <v>4377000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Shodlik Mehmonxona AJ</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>398545825</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>20208000338968394001</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Оплата по с/ф №9150 за поставленный товар</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>52178000</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B174" t="n">
+        <v>266</v>
+      </c>
+      <c r="C174" s="2" t="n">
+        <v>10445000</v>
+      </c>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Afrosiyob Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>278114821</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>20208000366791853001</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по дог. №99/26</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>41733000</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B175" t="n">
+        <v>267</v>
+      </c>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n">
+        <v>21877000</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>349190891</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>20208000409633144001</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №264/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>63610000</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B176" t="n">
+        <v>268</v>
+      </c>
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n">
+        <v>3396000</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Yulduz Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>277542784</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>20208000456435731001</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по договору №59/26 от 28.09.2026</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>67006000</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B177" t="n">
+        <v>269</v>
+      </c>
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n">
+        <v>2480000</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Yulduz Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>277542784</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>20208000456435731001</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>69486000</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B178" t="n">
+        <v>270</v>
+      </c>
+      <c r="C178" s="2" t="n">
+        <v>8510000</v>
+      </c>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Bekobod Meva Eksport MChJ</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>390941483</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>20208000537074600001</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №277/26</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>60976000</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B179" t="n">
+        <v>271</v>
+      </c>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n">
+        <v>1352000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Sharq Sut MChJ</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>349190891</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>20208000409633144001</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №75/26 от 29.09.2026</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>62328000</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B180" t="n">
+        <v>272</v>
+      </c>
+      <c r="C180" s="2" t="n">
+        <v>2628000</v>
+      </c>
+      <c r="D180" s="2" t="n"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Afrosiyob Poligraf AJ</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>278114821</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>20208000366791853001</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №6761</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>59700000</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B181" t="n">
+        <v>273</v>
+      </c>
+      <c r="C181" s="2" t="n">
         <v>300000</v>
       </c>
-      <c r="D169" s="2" t="n"/>
-      <c r="E169" t="inlineStr">
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" t="inlineStr">
         <is>
           <t>Navbahor Bank ATB</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>45994000900000001001</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>01121</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
-      <c r="J169" s="2" t="n">
+      <c r="J181" s="2" t="n">
         <v>59400000</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C170" s="4" t="n">
-        <v>738649000</v>
-      </c>
-      <c r="D170" s="4" t="n">
-        <v>738449000</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="C182" s="4" t="n">
+        <v>753634000</v>
+      </c>
+      <c r="D182" s="4" t="n">
+        <v>753434000</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C171" s="4" t="n">
+      <c r="C183" s="4" t="n">
         <v>59400000</v>
       </c>
-      <c r="D171" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
